--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table39.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table39.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -194,14 +194,14 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -510,7 +510,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -527,10 +527,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
@@ -541,7 +541,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -555,7 +555,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4"/>
+      <c r="A3" s="5"/>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
@@ -567,7 +567,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="4"/>
+      <c r="A4" s="5"/>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -579,7 +579,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="4"/>
+      <c r="A5" s="5"/>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
@@ -591,7 +591,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -605,7 +605,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="4"/>
+      <c r="A7" s="5"/>
       <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
@@ -617,7 +617,7 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -631,7 +631,7 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="4"/>
+      <c r="A9" s="5"/>
       <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
@@ -643,7 +643,7 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="4"/>
+      <c r="A10" s="5"/>
       <c r="B10" s="1" t="s">
         <v>14</v>
       </c>
